--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-HistoriqueDesGrossesses.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-HistoriqueDesGrossesses.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="98">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T14:36:02+00:00</t>
+    <t>2025-06-05T15:38:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -292,30 +292,17 @@
     <t>HistoriqueDesGrossesses.sousSection</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Section
-</t>
-  </si>
-  <si>
-    <t>Sous-sections</t>
-  </si>
-  <si>
-    <t>Section.sousSection</t>
-  </si>
-  <si>
-    <t>HistoriqueDesGrossesses.entree</t>
-  </si>
-  <si>
     <t xml:space="preserve">Base
 </t>
   </si>
   <si>
-    <t>Entrées</t>
-  </si>
-  <si>
-    <t>Section.entree</t>
-  </si>
-  <si>
-    <t>HistoriqueDesGrossesses.entry[x]</t>
+    <t>Sous-sections</t>
+  </si>
+  <si>
+    <t>Section.sousSection</t>
+  </si>
+  <si>
+    <t>HistoriqueDesGrossesses.entree</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ObservationGrossesse
@@ -323,6 +310,9 @@
   </si>
   <si>
     <t>Entrée Observation sur la grossesse ou Entrée Historique des grossesses</t>
+  </si>
+  <si>
+    <t>Section.entree</t>
   </si>
 </sst>
 </file>
@@ -624,7 +614,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ8"/>
+  <dimension ref="A1:AJ7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.93359375" customWidth="true" bestFit="true"/>
@@ -658,7 +648,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="27.6171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="16.86328125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1190,7 +1180,7 @@
         <v>73</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>72</v>
@@ -1287,7 +1277,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>74</v>
@@ -1371,106 +1361,6 @@
         <v>72</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-HistoriqueDesGrossesses.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-HistoriqueDesGrossesses.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05T15:38:56+00:00</t>
+    <t>2025-10-06T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
